--- a/task1.xlsx
+++ b/task1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\7 семестр\Имитационное моделирование\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEBF10B-4F1A-4423-8EAE-55E695A2C502}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008E7FD0-C102-41E9-B367-1014A3E0ABD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="20730" windowHeight="11160" xr2:uid="{DF026EEF-3546-4978-ACF6-D84FDFAC432B}"/>
+    <workbookView xWindow="11655" yWindow="600" windowWidth="8835" windowHeight="10785" xr2:uid="{DF026EEF-3546-4978-ACF6-D84FDFAC432B}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="K4" s="4">
         <f ca="1">J10+SQRT(J11)*(H24-G23/2)</f>
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -733,7 +733,7 @@
       </c>
       <c r="H12">
         <f ca="1">RANDBETWEEN(0,10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -757,7 +757,7 @@
       </c>
       <c r="H13">
         <f t="shared" ref="H13:H23" ca="1" si="6">RANDBETWEEN(0,10)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -781,7 +781,7 @@
       </c>
       <c r="H14">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -805,7 +805,7 @@
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -829,7 +829,7 @@
       </c>
       <c r="H16">
         <f t="shared" ca="1" si="6"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,7 +877,7 @@
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
       </c>
       <c r="H19">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,7 +925,7 @@
       </c>
       <c r="H20">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -949,7 +949,7 @@
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="6"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -997,7 +997,7 @@
       </c>
       <c r="H23">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H24">
         <f ca="1">SUM(H12:H23)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
